--- a/public/sheets/canadian-tire-stores.xlsx
+++ b/public/sheets/canadian-tire-stores.xlsx
@@ -13016,7 +13016,7 @@
         <v>702</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/public/sheets/canadian-tire-stores.xlsx
+++ b/public/sheets/canadian-tire-stores.xlsx
@@ -10534,38 +10534,38 @@
         <v>23</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="n">
+    <row r="66" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3" t="n">
         <v>608</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D66" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E66" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F66" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="G66" s="1" t="s">
+      <c r="G66" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="H66" s="1" t="n">
+      <c r="H66" s="3" t="n">
         <v>49.235016</v>
       </c>
-      <c r="I66" s="1" t="n">
+      <c r="I66" s="3" t="n">
         <v>-122.860456</v>
       </c>
-      <c r="J66" s="1" t="s">
+      <c r="J66" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="K66" s="1" t="s">
+      <c r="K66" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
         <v>1063</v>
       </c>
       <c r="K205" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20019,38 +20019,38 @@
         <v>23</v>
       </c>
     </row>
-    <row r="337" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A337" s="1" t="n">
+    <row r="337" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A337" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="B337" s="1" t="s">
+      <c r="B337" s="3" t="s">
         <v>1734</v>
       </c>
-      <c r="C337" s="1" t="s">
+      <c r="C337" s="3" t="s">
         <v>1735</v>
       </c>
-      <c r="D337" s="1" t="s">
+      <c r="D337" s="3" t="s">
         <v>1734</v>
       </c>
-      <c r="E337" s="1" t="s">
+      <c r="E337" s="3" t="s">
         <v>953</v>
       </c>
-      <c r="F337" s="1" t="s">
+      <c r="F337" s="3" t="s">
         <v>1736</v>
       </c>
-      <c r="G337" s="1" t="s">
+      <c r="G337" s="3" t="s">
         <v>1737</v>
       </c>
-      <c r="H337" s="1" t="n">
+      <c r="H337" s="3" t="n">
         <v>42.847527</v>
       </c>
-      <c r="I337" s="1" t="n">
+      <c r="I337" s="3" t="n">
         <v>-80.291736</v>
       </c>
-      <c r="J337" s="1" t="s">
+      <c r="J337" s="3" t="s">
         <v>1738</v>
       </c>
-      <c r="K337" s="1" t="s">
+      <c r="K337" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -21664,38 +21664,38 @@
         <v>23</v>
       </c>
     </row>
-    <row r="384" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A384" s="1" t="n">
+    <row r="384" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A384" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B384" s="1" t="s">
+      <c r="B384" s="3" t="s">
         <v>1975</v>
       </c>
-      <c r="C384" s="1" t="s">
+      <c r="C384" s="3" t="s">
         <v>1976</v>
       </c>
-      <c r="D384" s="1" t="s">
+      <c r="D384" s="3" t="s">
         <v>1975</v>
       </c>
-      <c r="E384" s="1" t="s">
+      <c r="E384" s="3" t="s">
         <v>1977</v>
       </c>
-      <c r="F384" s="1" t="s">
+      <c r="F384" s="3" t="s">
         <v>1978</v>
       </c>
-      <c r="G384" s="1" t="s">
+      <c r="G384" s="3" t="s">
         <v>1979</v>
       </c>
-      <c r="H384" s="1" t="n">
+      <c r="H384" s="3" t="n">
         <v>46.269094</v>
       </c>
-      <c r="I384" s="1" t="n">
+      <c r="I384" s="3" t="n">
         <v>-63.145017</v>
       </c>
-      <c r="J384" s="1" t="s">
+      <c r="J384" s="3" t="s">
         <v>1980</v>
       </c>
-      <c r="K384" s="1" t="s">
+      <c r="K384" s="3" t="s">
         <v>23</v>
       </c>
     </row>
@@ -24079,39 +24079,39 @@
         <v>23</v>
       </c>
     </row>
-    <row r="453" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A453" s="1" t="n">
+    <row r="453" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A453" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="B453" s="1" t="s">
+      <c r="B453" s="3" t="s">
         <v>2332</v>
       </c>
-      <c r="C453" s="1" t="s">
+      <c r="C453" s="3" t="s">
         <v>2333</v>
       </c>
-      <c r="D453" s="1" t="s">
+      <c r="D453" s="3" t="s">
         <v>2332</v>
       </c>
-      <c r="E453" s="1" t="s">
+      <c r="E453" s="3" t="s">
         <v>1988</v>
       </c>
-      <c r="F453" s="1" t="s">
+      <c r="F453" s="3" t="s">
         <v>2334</v>
       </c>
-      <c r="G453" s="1" t="s">
+      <c r="G453" s="3" t="s">
         <v>2335</v>
       </c>
-      <c r="H453" s="1" t="n">
+      <c r="H453" s="3" t="n">
         <v>48.46837</v>
       </c>
-      <c r="I453" s="1" t="n">
+      <c r="I453" s="3" t="n">
         <v>-68.514261</v>
       </c>
-      <c r="J453" s="1" t="s">
+      <c r="J453" s="3" t="s">
         <v>2336</v>
       </c>
-      <c r="K453" s="1" t="s">
-        <v>17</v>
+      <c r="K453" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="454" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/public/sheets/canadian-tire-stores.xlsx
+++ b/public/sheets/canadian-tire-stores.xlsx
@@ -7832,7 +7832,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7860,6 +7860,14 @@
       <sz val="11"/>
       <name val="Cambria"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -7911,7 +7919,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7924,11 +7932,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8819,38 +8835,38 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
+    <row r="17" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="n">
         <v>493</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="H17" s="1" t="n">
+      <c r="H17" s="3" t="n">
         <v>51.185803</v>
       </c>
-      <c r="I17" s="1" t="n">
+      <c r="I17" s="3" t="n">
         <v>-114.469496</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="K17" s="3" t="s">
         <v>23</v>
       </c>
     </row>
@@ -9309,40 +9325,41 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
+    <row r="31" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="n">
         <v>911</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="H31" s="1" t="n">
+      <c r="H31" s="3" t="n">
         <v>56.722547</v>
       </c>
-      <c r="I31" s="1" t="n">
+      <c r="I31" s="3" t="n">
         <v>-111.364206</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="J31" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="K31" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="L31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
@@ -9379,40 +9396,41 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
+    <row r="33" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="n">
         <v>344</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="H33" s="1" t="n">
+      <c r="H33" s="3" t="n">
         <v>55.173506</v>
       </c>
-      <c r="I33" s="1" t="n">
+      <c r="I33" s="3" t="n">
         <v>-118.848446</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="J33" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="K33" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="L33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
@@ -9519,40 +9537,41 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="n">
+    <row r="37" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="n">
         <v>448</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="H37" s="1" t="n">
+      <c r="H37" s="3" t="n">
         <v>53.269615</v>
       </c>
-      <c r="I37" s="1" t="n">
+      <c r="I37" s="3" t="n">
         <v>-113.567991</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="J37" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="K37" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="L37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
@@ -9589,75 +9608,77 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
+    <row r="39" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="n">
         <v>634</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="H39" s="1" t="n">
+      <c r="H39" s="3" t="n">
         <v>49.667402</v>
       </c>
-      <c r="I39" s="1" t="n">
+      <c r="I39" s="3" t="n">
         <v>-112.789577</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="J39" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="K39" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="n">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="n">
         <v>341</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="H40" s="1" t="n">
+      <c r="H40" s="3" t="n">
         <v>53.276213</v>
       </c>
-      <c r="I40" s="1" t="n">
+      <c r="I40" s="3" t="n">
         <v>-110.064874</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="J40" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="K40" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="L40" s="3"/>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="n">
@@ -10464,40 +10485,41 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="n">
+    <row r="64" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="3" t="n">
         <v>492</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E64" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="G64" s="1" t="s">
+      <c r="G64" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="H64" s="1" t="n">
+      <c r="H64" s="3" t="n">
         <v>49.294505</v>
       </c>
-      <c r="I64" s="1" t="n">
+      <c r="I64" s="3" t="n">
         <v>-117.654144</v>
       </c>
-      <c r="J64" s="1" t="s">
+      <c r="J64" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="K64" s="1" t="s">
+      <c r="K64" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="L64" s="3"/>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="n">
@@ -10534,75 +10556,76 @@
         <v>23</v>
       </c>
     </row>
-    <row r="66" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="3" t="n">
+    <row r="66" s="5" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="n">
         <v>608</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="D66" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="E66" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="F66" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="G66" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="H66" s="3" t="n">
+      <c r="H66" s="5" t="n">
         <v>49.235016</v>
       </c>
-      <c r="I66" s="3" t="n">
+      <c r="I66" s="5" t="n">
         <v>-122.860456</v>
       </c>
-      <c r="J66" s="3" t="s">
+      <c r="J66" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="n">
+      <c r="K66" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E67" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="G67" s="1" t="s">
+      <c r="G67" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="H67" s="1" t="n">
+      <c r="H67" s="3" t="n">
         <v>49.67266</v>
       </c>
-      <c r="I67" s="1" t="n">
+      <c r="I67" s="3" t="n">
         <v>-124.982277</v>
       </c>
-      <c r="J67" s="1" t="s">
+      <c r="J67" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="K67" s="1" t="s">
+      <c r="K67" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="L67" s="3"/>
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="n">
@@ -10884,75 +10907,77 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="n">
+    <row r="76" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3" t="n">
         <v>353</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D76" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E76" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="F76" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="G76" s="1" t="s">
+      <c r="G76" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="H76" s="1" t="n">
+      <c r="H76" s="3" t="n">
         <v>49.88827</v>
       </c>
-      <c r="I76" s="1" t="n">
+      <c r="I76" s="3" t="n">
         <v>-119.419644</v>
       </c>
-      <c r="J76" s="1" t="s">
+      <c r="J76" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="K76" s="1" t="s">
+      <c r="K76" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="n">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="3" t="n">
         <v>426</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D77" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E77" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="F77" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="G77" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="H77" s="1" t="n">
+      <c r="H77" s="3" t="n">
         <v>49.117672</v>
       </c>
-      <c r="I77" s="1" t="n">
+      <c r="I77" s="3" t="n">
         <v>-122.667203</v>
       </c>
-      <c r="J77" s="1" t="s">
+      <c r="J77" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="K77" s="1" t="s">
+      <c r="K77" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="L77" s="3"/>
     </row>
     <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="n">
@@ -11514,38 +11539,38 @@
         <v>17</v>
       </c>
     </row>
-    <row r="94" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="3" t="n">
+    <row r="94" s="5" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="5" t="n">
         <v>482</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C94" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="E94" s="3" t="s">
+      <c r="E94" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F94" s="3" t="s">
+      <c r="F94" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="G94" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="H94" s="3" t="n">
+      <c r="H94" s="5" t="n">
         <v>50.693784</v>
       </c>
-      <c r="I94" s="3" t="n">
+      <c r="I94" s="5" t="n">
         <v>-119.297595</v>
       </c>
-      <c r="J94" s="3" t="s">
+      <c r="J94" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="K94" s="3" t="s">
+      <c r="K94" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -11794,73 +11819,74 @@
         <v>23</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="n">
+    <row r="102" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="3" t="n">
         <v>665</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B102" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C102" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="D102" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="E102" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="F102" s="1" t="s">
+      <c r="F102" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="G102" s="1" t="s">
+      <c r="G102" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="H102" s="1" t="n">
+      <c r="H102" s="3" t="n">
         <v>49.088829</v>
       </c>
-      <c r="I102" s="1" t="n">
+      <c r="I102" s="3" t="n">
         <v>-117.627297</v>
       </c>
-      <c r="J102" s="1" t="s">
+      <c r="J102" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="K102" s="1" t="s">
+      <c r="K102" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="103" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="3" t="n">
+      <c r="L102" s="3"/>
+    </row>
+    <row r="103" s="5" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="5" t="n">
         <v>910</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C103" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="D103" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="E103" s="3" t="s">
+      <c r="E103" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F103" s="3" t="s">
+      <c r="F103" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="G103" s="3" t="s">
+      <c r="G103" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="H103" s="3" t="n">
+      <c r="H103" s="5" t="n">
         <v>49.042639</v>
       </c>
-      <c r="I103" s="3" t="n">
+      <c r="I103" s="5" t="n">
         <v>-123.08752</v>
       </c>
-      <c r="J103" s="3" t="s">
+      <c r="J103" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="K103" s="3" t="s">
+      <c r="K103" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -11899,40 +11925,41 @@
         <v>17</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="n">
+    <row r="105" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="3" t="n">
         <v>604</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B105" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C105" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D105" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E105" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="F105" s="1" t="s">
+      <c r="F105" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="G105" s="1" t="s">
+      <c r="G105" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="H105" s="1" t="n">
+      <c r="H105" s="3" t="n">
         <v>49.259515</v>
       </c>
-      <c r="I105" s="1" t="n">
+      <c r="I105" s="3" t="n">
         <v>-123.030986</v>
       </c>
-      <c r="J105" s="1" t="s">
+      <c r="J105" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="K105" s="1" t="s">
+      <c r="K105" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="L105" s="3"/>
     </row>
     <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="n">
@@ -12809,38 +12836,38 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="3" t="n">
+    <row r="131" s="5" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" s="5" t="s">
         <v>673</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="C131" s="5" t="s">
         <v>674</v>
       </c>
-      <c r="D131" s="3" t="s">
+      <c r="D131" s="5" t="s">
         <v>673</v>
       </c>
-      <c r="E131" s="3" t="s">
+      <c r="E131" s="5" t="s">
         <v>664</v>
       </c>
-      <c r="F131" s="3" t="s">
+      <c r="F131" s="5" t="s">
         <v>675</v>
       </c>
-      <c r="G131" s="3" t="s">
+      <c r="G131" s="5" t="s">
         <v>676</v>
       </c>
-      <c r="H131" s="3" t="n">
+      <c r="H131" s="5" t="n">
         <v>46.097385</v>
       </c>
-      <c r="I131" s="3" t="n">
+      <c r="I131" s="5" t="n">
         <v>-64.756197</v>
       </c>
-      <c r="J131" s="3" t="s">
+      <c r="J131" s="5" t="s">
         <v>677</v>
       </c>
-      <c r="K131" s="3" t="s">
+      <c r="K131" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13404,39 +13431,39 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="1" t="n">
+    <row r="148" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A148" s="3" t="n">
         <v>217</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="B148" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="C148" s="1" t="s">
+      <c r="C148" s="3" t="s">
         <v>762</v>
       </c>
-      <c r="D148" s="1" t="s">
+      <c r="D148" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="E148" s="1" t="s">
+      <c r="E148" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="F148" s="1" t="s">
+      <c r="F148" s="3" t="s">
         <v>764</v>
       </c>
-      <c r="G148" s="1" t="s">
+      <c r="G148" s="3" t="s">
         <v>765</v>
       </c>
-      <c r="H148" s="1" t="n">
+      <c r="H148" s="3" t="n">
         <v>47.723106</v>
       </c>
-      <c r="I148" s="1" t="n">
+      <c r="I148" s="3" t="n">
         <v>-53.240776</v>
       </c>
-      <c r="J148" s="1" t="s">
+      <c r="J148" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="K148" s="1" t="s">
-        <v>17</v>
+      <c r="K148" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13859,38 +13886,38 @@
         <v>17</v>
       </c>
     </row>
-    <row r="161" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A161" s="3" t="n">
+    <row r="161" s="5" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A161" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B161" s="3" t="s">
+      <c r="B161" s="5" t="s">
         <v>829</v>
       </c>
-      <c r="C161" s="3" t="s">
+      <c r="C161" s="5" t="s">
         <v>830</v>
       </c>
-      <c r="D161" s="3" t="s">
+      <c r="D161" s="5" t="s">
         <v>829</v>
       </c>
-      <c r="E161" s="3" t="s">
+      <c r="E161" s="5" t="s">
         <v>831</v>
       </c>
-      <c r="F161" s="3" t="s">
+      <c r="F161" s="5" t="s">
         <v>832</v>
       </c>
-      <c r="G161" s="3" t="s">
+      <c r="G161" s="5" t="s">
         <v>833</v>
       </c>
-      <c r="H161" s="3" t="n">
+      <c r="H161" s="5" t="n">
         <v>45.809747</v>
       </c>
-      <c r="I161" s="3" t="n">
+      <c r="I161" s="5" t="n">
         <v>-64.200389</v>
       </c>
-      <c r="J161" s="3" t="s">
+      <c r="J161" s="5" t="s">
         <v>834</v>
       </c>
-      <c r="K161" s="3" t="s">
+      <c r="K161" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13964,73 +13991,74 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="1" t="n">
+    <row r="164" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A164" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="B164" s="3" t="s">
         <v>846</v>
       </c>
-      <c r="C164" s="1" t="s">
+      <c r="C164" s="3" t="s">
         <v>847</v>
       </c>
-      <c r="D164" s="1" t="s">
+      <c r="D164" s="3" t="s">
         <v>846</v>
       </c>
-      <c r="E164" s="1" t="s">
+      <c r="E164" s="3" t="s">
         <v>831</v>
       </c>
-      <c r="F164" s="1" t="s">
+      <c r="F164" s="3" t="s">
         <v>848</v>
       </c>
-      <c r="G164" s="1" t="s">
+      <c r="G164" s="3" t="s">
         <v>849</v>
       </c>
-      <c r="H164" s="1" t="n">
+      <c r="H164" s="3" t="n">
         <v>44.39899</v>
       </c>
-      <c r="I164" s="1" t="n">
+      <c r="I164" s="3" t="n">
         <v>-64.534212</v>
       </c>
-      <c r="J164" s="1" t="s">
+      <c r="J164" s="3" t="s">
         <v>850</v>
       </c>
-      <c r="K164" s="1" t="s">
+      <c r="K164" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="165" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A165" s="3" t="n">
+      <c r="L164" s="3"/>
+    </row>
+    <row r="165" s="5" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A165" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="B165" s="3" t="s">
+      <c r="B165" s="5" t="s">
         <v>851</v>
       </c>
-      <c r="C165" s="3" t="s">
+      <c r="C165" s="5" t="s">
         <v>852</v>
       </c>
-      <c r="D165" s="3" t="s">
+      <c r="D165" s="5" t="s">
         <v>853</v>
       </c>
-      <c r="E165" s="3" t="s">
+      <c r="E165" s="5" t="s">
         <v>831</v>
       </c>
-      <c r="F165" s="3" t="s">
+      <c r="F165" s="5" t="s">
         <v>854</v>
       </c>
-      <c r="G165" s="3" t="s">
+      <c r="G165" s="5" t="s">
         <v>855</v>
       </c>
-      <c r="H165" s="3" t="n">
+      <c r="H165" s="5" t="n">
         <v>44.699661</v>
       </c>
-      <c r="I165" s="3" t="n">
+      <c r="I165" s="5" t="n">
         <v>-63.568853</v>
       </c>
-      <c r="J165" s="3" t="s">
+      <c r="J165" s="5" t="s">
         <v>856</v>
       </c>
-      <c r="K165" s="3" t="s">
+      <c r="K165" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -15049,40 +15077,41 @@
         <v>23</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="1" t="n">
+    <row r="195" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A195" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="B195" s="3" t="s">
         <v>1007</v>
       </c>
-      <c r="C195" s="1" t="s">
+      <c r="C195" s="3" t="s">
         <v>1008</v>
       </c>
-      <c r="D195" s="1" t="s">
+      <c r="D195" s="3" t="s">
         <v>1007</v>
       </c>
-      <c r="E195" s="1" t="s">
+      <c r="E195" s="3" t="s">
         <v>953</v>
       </c>
-      <c r="F195" s="1" t="s">
+      <c r="F195" s="3" t="s">
         <v>1009</v>
       </c>
-      <c r="G195" s="1" t="s">
+      <c r="G195" s="3" t="s">
         <v>1010</v>
       </c>
-      <c r="H195" s="1" t="n">
+      <c r="H195" s="3" t="n">
         <v>44.186243</v>
       </c>
-      <c r="I195" s="1" t="n">
+      <c r="I195" s="3" t="n">
         <v>-77.399738</v>
       </c>
-      <c r="J195" s="1" t="s">
+      <c r="J195" s="3" t="s">
         <v>1011</v>
       </c>
-      <c r="K195" s="1" t="s">
+      <c r="K195" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="L195" s="3"/>
     </row>
     <row r="196" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="n">
@@ -15189,39 +15218,39 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A199" s="1" t="n">
+    <row r="199" s="5" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A199" s="5" t="n">
         <v>206</v>
       </c>
-      <c r="B199" s="1" t="s">
+      <c r="B199" s="5" t="s">
         <v>1027</v>
       </c>
-      <c r="C199" s="1" t="s">
+      <c r="C199" s="5" t="s">
         <v>1028</v>
       </c>
-      <c r="D199" s="1" t="s">
+      <c r="D199" s="5" t="s">
         <v>1027</v>
       </c>
-      <c r="E199" s="1" t="s">
+      <c r="E199" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="F199" s="1" t="s">
+      <c r="F199" s="5" t="s">
         <v>1029</v>
       </c>
-      <c r="G199" s="1" t="s">
+      <c r="G199" s="5" t="s">
         <v>1030</v>
       </c>
-      <c r="H199" s="1" t="n">
+      <c r="H199" s="5" t="n">
         <v>45.042931</v>
       </c>
-      <c r="I199" s="1" t="n">
+      <c r="I199" s="5" t="n">
         <v>-79.325951</v>
       </c>
-      <c r="J199" s="1" t="s">
+      <c r="J199" s="5" t="s">
         <v>1031</v>
       </c>
-      <c r="K199" s="1" t="s">
-        <v>23</v>
+      <c r="K199" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15644,38 +15673,38 @@
         <v>17</v>
       </c>
     </row>
-    <row r="212" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A212" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B212" s="3" t="s">
+    <row r="212" s="5" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A212" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B212" s="5" t="s">
         <v>1095</v>
       </c>
-      <c r="C212" s="3" t="s">
+      <c r="C212" s="5" t="s">
         <v>1096</v>
       </c>
-      <c r="D212" s="3" t="s">
+      <c r="D212" s="5" t="s">
         <v>1095</v>
       </c>
-      <c r="E212" s="3" t="s">
+      <c r="E212" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="F212" s="3" t="s">
+      <c r="F212" s="5" t="s">
         <v>1097</v>
       </c>
-      <c r="G212" s="3" t="s">
+      <c r="G212" s="5" t="s">
         <v>1098</v>
       </c>
-      <c r="H212" s="3" t="n">
+      <c r="H212" s="5" t="n">
         <v>44.304545</v>
       </c>
-      <c r="I212" s="3" t="n">
+      <c r="I212" s="5" t="n">
         <v>-77.80465</v>
       </c>
-      <c r="J212" s="3" t="s">
+      <c r="J212" s="5" t="s">
         <v>1099</v>
       </c>
-      <c r="K212" s="3" t="s">
+      <c r="K212" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -16281,7 +16310,7 @@
       <c r="B230" s="1" t="s">
         <v>1184</v>
       </c>
-      <c r="C230" s="3" t="s">
+      <c r="C230" s="5" t="s">
         <v>1185</v>
       </c>
       <c r="D230" s="1" t="s">
@@ -16316,7 +16345,7 @@
       <c r="B231" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="C231" s="3" t="s">
+      <c r="C231" s="5" t="s">
         <v>1191</v>
       </c>
       <c r="D231" s="1" t="s">
@@ -16351,7 +16380,7 @@
       <c r="B232" s="1" t="s">
         <v>1195</v>
       </c>
-      <c r="C232" s="3" t="s">
+      <c r="C232" s="5" t="s">
         <v>1196</v>
       </c>
       <c r="D232" s="1" t="s">
@@ -16624,75 +16653,77 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A240" s="1" t="n">
+    <row r="240" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A240" s="3" t="n">
         <v>159</v>
       </c>
-      <c r="B240" s="1" t="s">
+      <c r="B240" s="3" t="s">
         <v>1236</v>
       </c>
-      <c r="C240" s="1" t="s">
+      <c r="C240" s="3" t="s">
         <v>1237</v>
       </c>
-      <c r="D240" s="1" t="s">
+      <c r="D240" s="3" t="s">
         <v>1236</v>
       </c>
-      <c r="E240" s="1" t="s">
+      <c r="E240" s="3" t="s">
         <v>953</v>
       </c>
-      <c r="F240" s="1" t="s">
+      <c r="F240" s="3" t="s">
         <v>1238</v>
       </c>
-      <c r="G240" s="1" t="s">
+      <c r="G240" s="3" t="s">
         <v>1239</v>
       </c>
-      <c r="H240" s="1" t="n">
+      <c r="H240" s="3" t="n">
         <v>43.650753</v>
       </c>
-      <c r="I240" s="1" t="n">
+      <c r="I240" s="3" t="n">
         <v>-79.888037</v>
       </c>
-      <c r="J240" s="1" t="s">
+      <c r="J240" s="3" t="s">
         <v>1240</v>
       </c>
-      <c r="K240" s="1" t="s">
+      <c r="K240" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="241" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A241" s="1" t="n">
+      <c r="L240" s="3"/>
+    </row>
+    <row r="241" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A241" s="3" t="n">
         <v>297</v>
       </c>
-      <c r="B241" s="1" t="s">
+      <c r="B241" s="3" t="s">
         <v>1241</v>
       </c>
-      <c r="C241" s="1" t="s">
+      <c r="C241" s="3" t="s">
         <v>1242</v>
       </c>
-      <c r="D241" s="1" t="s">
+      <c r="D241" s="3" t="s">
         <v>1243</v>
       </c>
-      <c r="E241" s="1" t="s">
+      <c r="E241" s="3" t="s">
         <v>953</v>
       </c>
-      <c r="F241" s="1" t="s">
+      <c r="F241" s="3" t="s">
         <v>1244</v>
       </c>
-      <c r="G241" s="1" t="s">
+      <c r="G241" s="3" t="s">
         <v>1245</v>
       </c>
-      <c r="H241" s="1" t="n">
+      <c r="H241" s="3" t="n">
         <v>45.435435</v>
       </c>
-      <c r="I241" s="1" t="n">
+      <c r="I241" s="3" t="n">
         <v>-75.606548</v>
       </c>
-      <c r="J241" s="1" t="s">
+      <c r="J241" s="3" t="s">
         <v>1246</v>
       </c>
-      <c r="K241" s="1" t="s">
+      <c r="K241" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="L241" s="3"/>
     </row>
     <row r="242" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="1" t="n">
@@ -17394,40 +17425,41 @@
         <v>23</v>
       </c>
     </row>
-    <row r="262" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A262" s="1" t="n">
+    <row r="262" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A262" s="3" t="n">
         <v>227</v>
       </c>
-      <c r="B262" s="1" t="s">
+      <c r="B262" s="3" t="s">
         <v>1350</v>
       </c>
-      <c r="C262" s="1" t="s">
+      <c r="C262" s="3" t="s">
         <v>1351</v>
       </c>
-      <c r="D262" s="1" t="s">
+      <c r="D262" s="3" t="s">
         <v>1350</v>
       </c>
-      <c r="E262" s="1" t="s">
+      <c r="E262" s="3" t="s">
         <v>953</v>
       </c>
-      <c r="F262" s="1" t="s">
+      <c r="F262" s="3" t="s">
         <v>1352</v>
       </c>
-      <c r="G262" s="1" t="s">
+      <c r="G262" s="3" t="s">
         <v>1353</v>
       </c>
-      <c r="H262" s="1" t="n">
+      <c r="H262" s="3" t="n">
         <v>45.02863</v>
       </c>
-      <c r="I262" s="1" t="n">
+      <c r="I262" s="3" t="n">
         <v>-75.63381</v>
       </c>
-      <c r="J262" s="1" t="s">
+      <c r="J262" s="3" t="s">
         <v>1354</v>
       </c>
-      <c r="K262" s="1" t="s">
+      <c r="K262" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="L262" s="3"/>
     </row>
     <row r="263" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="1" t="n">
@@ -17569,75 +17601,77 @@
         <v>17</v>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A267" s="1" t="n">
+    <row r="267" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A267" s="3" t="n">
         <v>417</v>
       </c>
-      <c r="B267" s="1" t="s">
+      <c r="B267" s="3" t="s">
         <v>1375</v>
       </c>
-      <c r="C267" s="1" t="s">
+      <c r="C267" s="3" t="s">
         <v>1376</v>
       </c>
-      <c r="D267" s="1" t="s">
+      <c r="D267" s="3" t="s">
         <v>1370</v>
       </c>
-      <c r="E267" s="1" t="s">
+      <c r="E267" s="3" t="s">
         <v>953</v>
       </c>
-      <c r="F267" s="1" t="s">
+      <c r="F267" s="3" t="s">
         <v>1377</v>
       </c>
-      <c r="G267" s="1" t="s">
+      <c r="G267" s="3" t="s">
         <v>1378</v>
       </c>
-      <c r="H267" s="1" t="n">
+      <c r="H267" s="3" t="n">
         <v>44.259938</v>
       </c>
-      <c r="I267" s="1" t="n">
+      <c r="I267" s="3" t="n">
         <v>-76.570126</v>
       </c>
-      <c r="J267" s="1" t="s">
+      <c r="J267" s="3" t="s">
         <v>1379</v>
       </c>
-      <c r="K267" s="1" t="s">
+      <c r="K267" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="268" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A268" s="1" t="n">
+      <c r="L267" s="3"/>
+    </row>
+    <row r="268" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A268" s="3" t="n">
         <v>694</v>
       </c>
-      <c r="B268" s="1" t="s">
+      <c r="B268" s="3" t="s">
         <v>1380</v>
       </c>
-      <c r="C268" s="1" t="s">
+      <c r="C268" s="3" t="s">
         <v>1381</v>
       </c>
-      <c r="D268" s="1" t="s">
+      <c r="D268" s="3" t="s">
         <v>1370</v>
       </c>
-      <c r="E268" s="1" t="s">
+      <c r="E268" s="3" t="s">
         <v>953</v>
       </c>
-      <c r="F268" s="1" t="s">
+      <c r="F268" s="3" t="s">
         <v>1382</v>
       </c>
-      <c r="G268" s="1" t="s">
+      <c r="G268" s="3" t="s">
         <v>1383</v>
       </c>
-      <c r="H268" s="1" t="n">
+      <c r="H268" s="3" t="n">
         <v>44.262785</v>
       </c>
-      <c r="I268" s="1" t="n">
+      <c r="I268" s="3" t="n">
         <v>-76.499919</v>
       </c>
-      <c r="J268" s="1" t="s">
+      <c r="J268" s="3" t="s">
         <v>1384</v>
       </c>
-      <c r="K268" s="1" t="s">
+      <c r="K268" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="L268" s="3"/>
     </row>
     <row r="269" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="n">
@@ -19144,38 +19178,38 @@
         <v>17</v>
       </c>
     </row>
-    <row r="312" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A312" s="3" t="n">
+    <row r="312" s="5" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A312" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="B312" s="3" t="s">
+      <c r="B312" s="5" t="s">
         <v>1608</v>
       </c>
-      <c r="C312" s="3" t="s">
+      <c r="C312" s="5" t="s">
         <v>1609</v>
       </c>
-      <c r="D312" s="3" t="s">
+      <c r="D312" s="5" t="s">
         <v>1608</v>
       </c>
-      <c r="E312" s="3" t="s">
+      <c r="E312" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="F312" s="3" t="s">
+      <c r="F312" s="5" t="s">
         <v>1610</v>
       </c>
-      <c r="G312" s="3" t="s">
+      <c r="G312" s="5" t="s">
         <v>1611</v>
       </c>
-      <c r="H312" s="3" t="n">
+      <c r="H312" s="5" t="n">
         <v>44.573868</v>
       </c>
-      <c r="I312" s="3" t="n">
+      <c r="I312" s="5" t="n">
         <v>-80.914704</v>
       </c>
-      <c r="J312" s="3" t="s">
+      <c r="J312" s="5" t="s">
         <v>1612</v>
       </c>
-      <c r="K312" s="3" t="s">
+      <c r="K312" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -19319,40 +19353,41 @@
         <v>23</v>
       </c>
     </row>
-    <row r="317" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A317" s="1" t="n">
+    <row r="317" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A317" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="B317" s="1" t="s">
+      <c r="B317" s="3" t="s">
         <v>1633</v>
       </c>
-      <c r="C317" s="1" t="s">
+      <c r="C317" s="3" t="s">
         <v>1634</v>
       </c>
-      <c r="D317" s="1" t="s">
+      <c r="D317" s="3" t="s">
         <v>1633</v>
       </c>
-      <c r="E317" s="1" t="s">
+      <c r="E317" s="3" t="s">
         <v>953</v>
       </c>
-      <c r="F317" s="1" t="s">
+      <c r="F317" s="3" t="s">
         <v>1635</v>
       </c>
-      <c r="G317" s="1" t="s">
+      <c r="G317" s="3" t="s">
         <v>1636</v>
       </c>
-      <c r="H317" s="1" t="n">
+      <c r="H317" s="3" t="n">
         <v>44.281443</v>
       </c>
-      <c r="I317" s="1" t="n">
+      <c r="I317" s="3" t="n">
         <v>-78.351622</v>
       </c>
-      <c r="J317" s="1" t="s">
+      <c r="J317" s="3" t="s">
         <v>1637</v>
       </c>
-      <c r="K317" s="1" t="s">
+      <c r="K317" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="L317" s="3"/>
     </row>
     <row r="318" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="3" t="n">
@@ -19984,73 +20019,74 @@
         <v>17</v>
       </c>
     </row>
-    <row r="336" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A336" s="1" t="n">
+    <row r="336" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A336" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="B336" s="1" t="s">
+      <c r="B336" s="3" t="s">
         <v>1728</v>
       </c>
-      <c r="C336" s="1" t="s">
+      <c r="C336" s="3" t="s">
         <v>1729</v>
       </c>
-      <c r="D336" s="1" t="s">
+      <c r="D336" s="3" t="s">
         <v>1730</v>
       </c>
-      <c r="E336" s="1" t="s">
+      <c r="E336" s="3" t="s">
         <v>953</v>
       </c>
-      <c r="F336" s="1" t="s">
+      <c r="F336" s="3" t="s">
         <v>1731</v>
       </c>
-      <c r="G336" s="1" t="s">
+      <c r="G336" s="3" t="s">
         <v>1732</v>
       </c>
-      <c r="H336" s="1" t="n">
+      <c r="H336" s="3" t="n">
         <v>44.631435</v>
       </c>
-      <c r="I336" s="1" t="n">
+      <c r="I336" s="3" t="n">
         <v>-79.435303</v>
       </c>
-      <c r="J336" s="1" t="s">
+      <c r="J336" s="3" t="s">
         <v>1733</v>
       </c>
-      <c r="K336" s="1" t="s">
+      <c r="K336" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="337" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A337" s="3" t="n">
+      <c r="L336" s="3"/>
+    </row>
+    <row r="337" s="5" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A337" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="B337" s="3" t="s">
+      <c r="B337" s="5" t="s">
         <v>1734</v>
       </c>
-      <c r="C337" s="3" t="s">
+      <c r="C337" s="5" t="s">
         <v>1735</v>
       </c>
-      <c r="D337" s="3" t="s">
+      <c r="D337" s="5" t="s">
         <v>1734</v>
       </c>
-      <c r="E337" s="3" t="s">
+      <c r="E337" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="F337" s="3" t="s">
+      <c r="F337" s="5" t="s">
         <v>1736</v>
       </c>
-      <c r="G337" s="3" t="s">
+      <c r="G337" s="5" t="s">
         <v>1737</v>
       </c>
-      <c r="H337" s="3" t="n">
+      <c r="H337" s="5" t="n">
         <v>42.847527</v>
       </c>
-      <c r="I337" s="3" t="n">
+      <c r="I337" s="5" t="n">
         <v>-80.291736</v>
       </c>
-      <c r="J337" s="3" t="s">
+      <c r="J337" s="5" t="s">
         <v>1738</v>
       </c>
-      <c r="K337" s="3" t="s">
+      <c r="K337" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -20299,40 +20335,41 @@
         <v>17</v>
       </c>
     </row>
-    <row r="345" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A345" s="1" t="n">
+    <row r="345" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A345" s="3" t="n">
         <v>103</v>
       </c>
-      <c r="B345" s="1" t="s">
+      <c r="B345" s="3" t="s">
         <v>1774</v>
       </c>
-      <c r="C345" s="1" t="s">
+      <c r="C345" s="3" t="s">
         <v>1775</v>
       </c>
-      <c r="D345" s="1" t="s">
+      <c r="D345" s="3" t="s">
         <v>1774</v>
       </c>
-      <c r="E345" s="1" t="s">
+      <c r="E345" s="3" t="s">
         <v>953</v>
       </c>
-      <c r="F345" s="1" t="s">
+      <c r="F345" s="3" t="s">
         <v>1776</v>
       </c>
-      <c r="G345" s="1" t="s">
+      <c r="G345" s="3" t="s">
         <v>1777</v>
       </c>
-      <c r="H345" s="1" t="n">
+      <c r="H345" s="3" t="n">
         <v>43.369673</v>
       </c>
-      <c r="I345" s="1" t="n">
+      <c r="I345" s="3" t="n">
         <v>-80.943441</v>
       </c>
-      <c r="J345" s="1" t="s">
+      <c r="J345" s="3" t="s">
         <v>1778</v>
       </c>
-      <c r="K345" s="1" t="s">
+      <c r="K345" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="L345" s="3"/>
     </row>
     <row r="346" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="1" t="n">
@@ -20544,38 +20581,38 @@
         <v>23</v>
       </c>
     </row>
-    <row r="352" s="1" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A352" s="1" t="n">
+    <row r="352" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A352" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="B352" s="1" t="s">
+      <c r="B352" s="3" t="s">
         <v>1812</v>
       </c>
-      <c r="C352" s="1" t="s">
+      <c r="C352" s="3" t="s">
         <v>1813</v>
       </c>
-      <c r="D352" s="1" t="s">
+      <c r="D352" s="3" t="s">
         <v>1808</v>
       </c>
-      <c r="E352" s="1" t="s">
+      <c r="E352" s="3" t="s">
         <v>953</v>
       </c>
-      <c r="F352" s="1" t="s">
+      <c r="F352" s="3" t="s">
         <v>1814</v>
       </c>
-      <c r="G352" s="1" t="s">
+      <c r="G352" s="3" t="s">
         <v>1815</v>
       </c>
-      <c r="H352" s="1" t="n">
+      <c r="H352" s="3" t="n">
         <v>48.40311</v>
       </c>
-      <c r="I352" s="1" t="n">
+      <c r="I352" s="3" t="n">
         <v>-89.239975</v>
       </c>
-      <c r="J352" s="1" t="s">
+      <c r="J352" s="3" t="s">
         <v>1816</v>
       </c>
-      <c r="K352" s="1" t="s">
+      <c r="K352" s="3" t="s">
         <v>23</v>
       </c>
     </row>
@@ -20684,388 +20721,388 @@
         <v>23</v>
       </c>
     </row>
-    <row r="356" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A356" s="4" t="n">
+    <row r="356" s="6" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A356" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B356" s="4" t="s">
+      <c r="B356" s="6" t="s">
         <v>1832</v>
       </c>
-      <c r="C356" s="4" t="s">
+      <c r="C356" s="6" t="s">
         <v>1833</v>
       </c>
-      <c r="D356" s="4" t="s">
+      <c r="D356" s="6" t="s">
         <v>1834</v>
       </c>
-      <c r="E356" s="4" t="s">
+      <c r="E356" s="6" t="s">
         <v>953</v>
       </c>
-      <c r="F356" s="4" t="s">
+      <c r="F356" s="6" t="s">
         <v>1835</v>
       </c>
-      <c r="G356" s="4" t="s">
+      <c r="G356" s="6" t="s">
         <v>1836</v>
       </c>
-      <c r="H356" s="4" t="n">
+      <c r="H356" s="6" t="n">
         <v>43.716128</v>
       </c>
-      <c r="I356" s="4" t="n">
+      <c r="I356" s="6" t="n">
         <v>-79.447852</v>
       </c>
-      <c r="J356" s="4" t="s">
+      <c r="J356" s="6" t="s">
         <v>1837</v>
       </c>
-      <c r="K356" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="357" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A357" s="4" t="n">
+      <c r="K356" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="357" s="6" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A357" s="6" t="n">
         <v>126</v>
       </c>
-      <c r="B357" s="4" t="s">
+      <c r="B357" s="6" t="s">
         <v>1838</v>
       </c>
-      <c r="C357" s="4" t="s">
+      <c r="C357" s="6" t="s">
         <v>1839</v>
       </c>
-      <c r="D357" s="4" t="s">
+      <c r="D357" s="6" t="s">
         <v>1834</v>
       </c>
-      <c r="E357" s="4" t="s">
+      <c r="E357" s="6" t="s">
         <v>953</v>
       </c>
-      <c r="F357" s="4" t="s">
+      <c r="F357" s="6" t="s">
         <v>1840</v>
       </c>
-      <c r="G357" s="4" t="s">
+      <c r="G357" s="6" t="s">
         <v>1841</v>
       </c>
-      <c r="H357" s="4" t="n">
+      <c r="H357" s="6" t="n">
         <v>43.796086</v>
       </c>
-      <c r="I357" s="4" t="n">
+      <c r="I357" s="6" t="n">
         <v>-79.423862</v>
       </c>
-      <c r="J357" s="4" t="s">
+      <c r="J357" s="6" t="s">
         <v>1842</v>
       </c>
-      <c r="K357" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="358" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A358" s="4" t="n">
+      <c r="K357" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="358" s="6" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A358" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="B358" s="4" t="s">
+      <c r="B358" s="6" t="s">
         <v>1843</v>
       </c>
-      <c r="C358" s="4" t="s">
+      <c r="C358" s="6" t="s">
         <v>1844</v>
       </c>
-      <c r="D358" s="4" t="s">
+      <c r="D358" s="6" t="s">
         <v>1834</v>
       </c>
-      <c r="E358" s="4" t="s">
+      <c r="E358" s="6" t="s">
         <v>953</v>
       </c>
-      <c r="F358" s="4" t="s">
+      <c r="F358" s="6" t="s">
         <v>1845</v>
       </c>
-      <c r="G358" s="4" t="s">
+      <c r="G358" s="6" t="s">
         <v>1846</v>
       </c>
-      <c r="H358" s="4" t="n">
+      <c r="H358" s="6" t="n">
         <v>43.673711</v>
       </c>
-      <c r="I358" s="4" t="n">
+      <c r="I358" s="6" t="n">
         <v>-79.387593</v>
       </c>
-      <c r="J358" s="4" t="s">
+      <c r="J358" s="6" t="s">
         <v>1847</v>
       </c>
-      <c r="K358" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="359" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A359" s="4" t="n">
+      <c r="K358" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="359" s="6" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A359" s="6" t="n">
         <v>182</v>
       </c>
-      <c r="B359" s="4" t="s">
+      <c r="B359" s="6" t="s">
         <v>1848</v>
       </c>
-      <c r="C359" s="4" t="s">
+      <c r="C359" s="6" t="s">
         <v>1849</v>
       </c>
-      <c r="D359" s="4" t="s">
+      <c r="D359" s="6" t="s">
         <v>1834</v>
       </c>
-      <c r="E359" s="4" t="s">
+      <c r="E359" s="6" t="s">
         <v>953</v>
       </c>
-      <c r="F359" s="4" t="s">
+      <c r="F359" s="6" t="s">
         <v>1850</v>
       </c>
-      <c r="G359" s="4" t="s">
+      <c r="G359" s="6" t="s">
         <v>1851</v>
       </c>
-      <c r="H359" s="4" t="n">
+      <c r="H359" s="6" t="n">
         <v>43.670599</v>
       </c>
-      <c r="I359" s="4" t="n">
+      <c r="I359" s="6" t="n">
         <v>-79.471761</v>
       </c>
-      <c r="J359" s="4" t="s">
+      <c r="J359" s="6" t="s">
         <v>1852</v>
       </c>
-      <c r="K359" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="360" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A360" s="4" t="n">
+      <c r="K359" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="360" s="6" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A360" s="6" t="n">
         <v>192</v>
       </c>
-      <c r="B360" s="4" t="s">
+      <c r="B360" s="6" t="s">
         <v>1853</v>
       </c>
-      <c r="C360" s="4" t="s">
+      <c r="C360" s="6" t="s">
         <v>1854</v>
       </c>
-      <c r="D360" s="4" t="s">
+      <c r="D360" s="6" t="s">
         <v>1834</v>
       </c>
-      <c r="E360" s="4" t="s">
+      <c r="E360" s="6" t="s">
         <v>953</v>
       </c>
-      <c r="F360" s="4" t="s">
+      <c r="F360" s="6" t="s">
         <v>1855</v>
       </c>
-      <c r="G360" s="4" t="s">
+      <c r="G360" s="6" t="s">
         <v>1856</v>
       </c>
-      <c r="H360" s="4" t="n">
+      <c r="H360" s="6" t="n">
         <v>43.769037</v>
       </c>
-      <c r="I360" s="4" t="n">
+      <c r="I360" s="6" t="n">
         <v>-79.371951</v>
       </c>
-      <c r="J360" s="4" t="s">
+      <c r="J360" s="6" t="s">
         <v>1857</v>
       </c>
-      <c r="K360" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="361" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A361" s="4" t="n">
+      <c r="K360" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="361" s="6" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A361" s="6" t="n">
         <v>214</v>
       </c>
-      <c r="B361" s="4" t="s">
+      <c r="B361" s="6" t="s">
         <v>1858</v>
       </c>
-      <c r="C361" s="4" t="s">
+      <c r="C361" s="6" t="s">
         <v>1859</v>
       </c>
-      <c r="D361" s="4" t="s">
+      <c r="D361" s="6" t="s">
         <v>1834</v>
       </c>
-      <c r="E361" s="4" t="s">
+      <c r="E361" s="6" t="s">
         <v>953</v>
       </c>
-      <c r="F361" s="4" t="s">
+      <c r="F361" s="6" t="s">
         <v>1860</v>
       </c>
-      <c r="G361" s="4" t="s">
+      <c r="G361" s="6" t="s">
         <v>1861</v>
       </c>
-      <c r="H361" s="4" t="n">
+      <c r="H361" s="6" t="n">
         <v>43.693368</v>
       </c>
-      <c r="I361" s="4" t="n">
+      <c r="I361" s="6" t="n">
         <v>-79.467035</v>
       </c>
-      <c r="J361" s="4" t="s">
+      <c r="J361" s="6" t="s">
         <v>1862</v>
       </c>
-      <c r="K361" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="362" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A362" s="4" t="n">
+      <c r="K361" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="362" s="6" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A362" s="6" t="n">
         <v>273</v>
       </c>
-      <c r="B362" s="4" t="s">
+      <c r="B362" s="6" t="s">
         <v>1863</v>
       </c>
-      <c r="C362" s="4" t="s">
+      <c r="C362" s="6" t="s">
         <v>1864</v>
       </c>
-      <c r="D362" s="4" t="s">
+      <c r="D362" s="6" t="s">
         <v>1834</v>
       </c>
-      <c r="E362" s="4" t="s">
+      <c r="E362" s="6" t="s">
         <v>953</v>
       </c>
-      <c r="F362" s="4" t="s">
+      <c r="F362" s="6" t="s">
         <v>1865</v>
       </c>
-      <c r="G362" s="4" t="s">
+      <c r="G362" s="6" t="s">
         <v>1866</v>
       </c>
-      <c r="H362" s="4" t="n">
+      <c r="H362" s="6" t="n">
         <v>43.688217</v>
       </c>
-      <c r="I362" s="4" t="n">
+      <c r="I362" s="6" t="n">
         <v>-79.298308</v>
       </c>
-      <c r="J362" s="4" t="s">
+      <c r="J362" s="6" t="s">
         <v>1867</v>
       </c>
-      <c r="K362" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="363" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A363" s="4" t="n">
+      <c r="K362" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="363" s="6" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A363" s="6" t="n">
         <v>459</v>
       </c>
-      <c r="B363" s="4" t="s">
+      <c r="B363" s="6" t="s">
         <v>1868</v>
       </c>
-      <c r="C363" s="4" t="s">
+      <c r="C363" s="6" t="s">
         <v>1869</v>
       </c>
-      <c r="D363" s="4" t="s">
+      <c r="D363" s="6" t="s">
         <v>1834</v>
       </c>
-      <c r="E363" s="4" t="s">
+      <c r="E363" s="6" t="s">
         <v>953</v>
       </c>
-      <c r="F363" s="4" t="s">
+      <c r="F363" s="6" t="s">
         <v>1870</v>
       </c>
-      <c r="G363" s="4" t="s">
+      <c r="G363" s="6" t="s">
         <v>1871</v>
       </c>
-      <c r="H363" s="4" t="n">
+      <c r="H363" s="6" t="n">
         <v>43.712534</v>
       </c>
-      <c r="I363" s="4" t="n">
+      <c r="I363" s="6" t="n">
         <v>-79.363368</v>
       </c>
-      <c r="J363" s="4" t="s">
+      <c r="J363" s="6" t="s">
         <v>1872</v>
       </c>
-      <c r="K363" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="364" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A364" s="4" t="n">
+      <c r="K363" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="364" s="6" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A364" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="B364" s="4" t="s">
+      <c r="B364" s="6" t="s">
         <v>1873</v>
       </c>
-      <c r="C364" s="4" t="s">
+      <c r="C364" s="6" t="s">
         <v>1874</v>
       </c>
-      <c r="D364" s="4" t="s">
+      <c r="D364" s="6" t="s">
         <v>1834</v>
       </c>
-      <c r="E364" s="4" t="s">
+      <c r="E364" s="6" t="s">
         <v>953</v>
       </c>
-      <c r="F364" s="4" t="s">
+      <c r="F364" s="6" t="s">
         <v>1875</v>
       </c>
-      <c r="G364" s="4" t="s">
+      <c r="G364" s="6" t="s">
         <v>1876</v>
       </c>
-      <c r="H364" s="4" t="n">
+      <c r="H364" s="6" t="n">
         <v>43.655535</v>
       </c>
-      <c r="I364" s="4" t="n">
+      <c r="I364" s="6" t="n">
         <v>-79.383382</v>
       </c>
-      <c r="J364" s="4" t="s">
+      <c r="J364" s="6" t="s">
         <v>1877</v>
       </c>
-      <c r="K364" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="365" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A365" s="4" t="n">
+      <c r="K364" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="365" s="6" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A365" s="6" t="n">
         <v>621</v>
       </c>
-      <c r="B365" s="4" t="s">
+      <c r="B365" s="6" t="s">
         <v>1878</v>
       </c>
-      <c r="C365" s="4" t="s">
+      <c r="C365" s="6" t="s">
         <v>1879</v>
       </c>
-      <c r="D365" s="4" t="s">
+      <c r="D365" s="6" t="s">
         <v>1834</v>
       </c>
-      <c r="E365" s="4" t="s">
+      <c r="E365" s="6" t="s">
         <v>953</v>
       </c>
-      <c r="F365" s="4" t="s">
+      <c r="F365" s="6" t="s">
         <v>1880</v>
       </c>
-      <c r="G365" s="4" t="s">
+      <c r="G365" s="6" t="s">
         <v>1881</v>
       </c>
-      <c r="H365" s="4" t="n">
+      <c r="H365" s="6" t="n">
         <v>43.639935</v>
       </c>
-      <c r="I365" s="4" t="n">
+      <c r="I365" s="6" t="n">
         <v>-79.423492</v>
       </c>
-      <c r="J365" s="4" t="s">
+      <c r="J365" s="6" t="s">
         <v>1882</v>
       </c>
-      <c r="K365" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="366" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A366" s="4" t="n">
+      <c r="K365" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="366" s="6" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A366" s="6" t="n">
         <v>654</v>
       </c>
-      <c r="B366" s="4" t="s">
+      <c r="B366" s="6" t="s">
         <v>1883</v>
       </c>
-      <c r="C366" s="4" t="s">
+      <c r="C366" s="6" t="s">
         <v>1884</v>
       </c>
-      <c r="D366" s="4" t="s">
+      <c r="D366" s="6" t="s">
         <v>1834</v>
       </c>
-      <c r="E366" s="4" t="s">
+      <c r="E366" s="6" t="s">
         <v>953</v>
       </c>
-      <c r="F366" s="4" t="s">
+      <c r="F366" s="6" t="s">
         <v>1885</v>
       </c>
-      <c r="G366" s="4" t="s">
+      <c r="G366" s="6" t="s">
         <v>1886</v>
       </c>
-      <c r="H366" s="4" t="n">
+      <c r="H366" s="6" t="n">
         <v>43.658096</v>
       </c>
-      <c r="I366" s="4" t="n">
+      <c r="I366" s="6" t="n">
         <v>-79.328737</v>
       </c>
-      <c r="J366" s="4" t="s">
+      <c r="J366" s="6" t="s">
         <v>1887</v>
       </c>
-      <c r="K366" s="4" t="s">
+      <c r="K366" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -21279,38 +21316,38 @@
         <v>17</v>
       </c>
     </row>
-    <row r="373" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A373" s="3" t="n">
+    <row r="373" s="5" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A373" s="5" t="n">
         <v>251</v>
       </c>
-      <c r="B373" s="3" t="s">
+      <c r="B373" s="5" t="s">
         <v>1919</v>
       </c>
-      <c r="C373" s="3" t="s">
+      <c r="C373" s="5" t="s">
         <v>1920</v>
       </c>
-      <c r="D373" s="3" t="s">
+      <c r="D373" s="5" t="s">
         <v>1919</v>
       </c>
-      <c r="E373" s="3" t="s">
+      <c r="E373" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="F373" s="3" t="s">
+      <c r="F373" s="5" t="s">
         <v>1921</v>
       </c>
-      <c r="G373" s="3" t="s">
+      <c r="G373" s="5" t="s">
         <v>1922</v>
       </c>
-      <c r="H373" s="3" t="n">
+      <c r="H373" s="5" t="n">
         <v>43.485236</v>
       </c>
-      <c r="I373" s="3" t="n">
+      <c r="I373" s="5" t="n">
         <v>-80.523074</v>
       </c>
-      <c r="J373" s="3" t="s">
+      <c r="J373" s="5" t="s">
         <v>1923</v>
       </c>
-      <c r="K373" s="3" t="s">
+      <c r="K373" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -23904,73 +23941,73 @@
         <v>17</v>
       </c>
     </row>
-    <row r="448" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A448" s="3" t="n">
+    <row r="448" s="5" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A448" s="5" t="n">
         <v>184</v>
       </c>
-      <c r="B448" s="3" t="s">
+      <c r="B448" s="5" t="s">
         <v>2307</v>
       </c>
-      <c r="C448" s="3" t="s">
+      <c r="C448" s="5" t="s">
         <v>2308</v>
       </c>
-      <c r="D448" s="3" t="s">
+      <c r="D448" s="5" t="s">
         <v>2303</v>
       </c>
-      <c r="E448" s="3" t="s">
+      <c r="E448" s="5" t="s">
         <v>1988</v>
       </c>
-      <c r="F448" s="3" t="s">
+      <c r="F448" s="5" t="s">
         <v>2309</v>
       </c>
-      <c r="G448" s="3" t="s">
+      <c r="G448" s="5" t="s">
         <v>2310</v>
       </c>
-      <c r="H448" s="3" t="n">
+      <c r="H448" s="5" t="n">
         <v>46.872718</v>
       </c>
-      <c r="I448" s="3" t="n">
+      <c r="I448" s="5" t="n">
         <v>-71.202226</v>
       </c>
-      <c r="J448" s="3" t="s">
+      <c r="J448" s="5" t="s">
         <v>2311</v>
       </c>
-      <c r="K448" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="449" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A449" s="3" t="n">
+      <c r="K448" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="449" s="5" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A449" s="5" t="n">
         <v>245</v>
       </c>
-      <c r="B449" s="3" t="s">
+      <c r="B449" s="5" t="s">
         <v>2312</v>
       </c>
-      <c r="C449" s="3" t="s">
+      <c r="C449" s="5" t="s">
         <v>2313</v>
       </c>
-      <c r="D449" s="3" t="s">
+      <c r="D449" s="5" t="s">
         <v>2303</v>
       </c>
-      <c r="E449" s="3" t="s">
+      <c r="E449" s="5" t="s">
         <v>1988</v>
       </c>
-      <c r="F449" s="3" t="s">
+      <c r="F449" s="5" t="s">
         <v>2314</v>
       </c>
-      <c r="G449" s="3" t="s">
+      <c r="G449" s="5" t="s">
         <v>2315</v>
       </c>
-      <c r="H449" s="3" t="n">
+      <c r="H449" s="5" t="n">
         <v>46.767937</v>
       </c>
-      <c r="I449" s="3" t="n">
+      <c r="I449" s="5" t="n">
         <v>-71.291265</v>
       </c>
-      <c r="J449" s="3" t="s">
+      <c r="J449" s="5" t="s">
         <v>2316</v>
       </c>
-      <c r="K449" s="3" t="s">
+      <c r="K449" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -24079,38 +24116,38 @@
         <v>23</v>
       </c>
     </row>
-    <row r="453" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A453" s="3" t="n">
+    <row r="453" s="5" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A453" s="5" t="n">
         <v>320</v>
       </c>
-      <c r="B453" s="3" t="s">
+      <c r="B453" s="5" t="s">
         <v>2332</v>
       </c>
-      <c r="C453" s="3" t="s">
+      <c r="C453" s="5" t="s">
         <v>2333</v>
       </c>
-      <c r="D453" s="3" t="s">
+      <c r="D453" s="5" t="s">
         <v>2332</v>
       </c>
-      <c r="E453" s="3" t="s">
+      <c r="E453" s="5" t="s">
         <v>1988</v>
       </c>
-      <c r="F453" s="3" t="s">
+      <c r="F453" s="5" t="s">
         <v>2334</v>
       </c>
-      <c r="G453" s="3" t="s">
+      <c r="G453" s="5" t="s">
         <v>2335</v>
       </c>
-      <c r="H453" s="3" t="n">
+      <c r="H453" s="5" t="n">
         <v>48.46837</v>
       </c>
-      <c r="I453" s="3" t="n">
+      <c r="I453" s="5" t="n">
         <v>-68.514261</v>
       </c>
-      <c r="J453" s="3" t="s">
+      <c r="J453" s="5" t="s">
         <v>2336</v>
       </c>
-      <c r="K453" s="3" t="s">
+      <c r="K453" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -25234,40 +25271,41 @@
         <v>17</v>
       </c>
     </row>
-    <row r="486" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A486" s="1" t="n">
+    <row r="486" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A486" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="B486" s="1" t="s">
+      <c r="B486" s="3" t="s">
         <v>2511</v>
       </c>
-      <c r="C486" s="1" t="s">
+      <c r="C486" s="3" t="s">
         <v>2512</v>
       </c>
-      <c r="D486" s="1" t="s">
+      <c r="D486" s="3" t="s">
         <v>2511</v>
       </c>
-      <c r="E486" s="1" t="s">
+      <c r="E486" s="3" t="s">
         <v>2513</v>
       </c>
-      <c r="F486" s="1" t="s">
+      <c r="F486" s="3" t="s">
         <v>2514</v>
       </c>
-      <c r="G486" s="1" t="s">
+      <c r="G486" s="3" t="s">
         <v>2515</v>
       </c>
-      <c r="H486" s="1" t="n">
+      <c r="H486" s="3" t="n">
         <v>49.145708</v>
       </c>
-      <c r="I486" s="1" t="n">
+      <c r="I486" s="3" t="n">
         <v>-102.974575</v>
       </c>
-      <c r="J486" s="1" t="s">
+      <c r="J486" s="3" t="s">
         <v>2516</v>
       </c>
-      <c r="K486" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="K486" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L486" s="3"/>
     </row>
     <row r="487" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="1" t="n">
@@ -25514,40 +25552,41 @@
         <v>23</v>
       </c>
     </row>
-    <row r="494" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A494" s="1" t="n">
+    <row r="494" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A494" s="3" t="n">
         <v>275</v>
       </c>
-      <c r="B494" s="1" t="s">
+      <c r="B494" s="3" t="s">
         <v>2552</v>
       </c>
-      <c r="C494" s="1" t="s">
+      <c r="C494" s="3" t="s">
         <v>2553</v>
       </c>
-      <c r="D494" s="1" t="s">
+      <c r="D494" s="3" t="s">
         <v>2554</v>
       </c>
-      <c r="E494" s="1" t="s">
+      <c r="E494" s="3" t="s">
         <v>2513</v>
       </c>
-      <c r="F494" s="1" t="s">
+      <c r="F494" s="3" t="s">
         <v>2555</v>
       </c>
-      <c r="G494" s="1" t="s">
+      <c r="G494" s="3" t="s">
         <v>2556</v>
       </c>
-      <c r="H494" s="1" t="n">
+      <c r="H494" s="3" t="n">
         <v>50.467598</v>
       </c>
-      <c r="I494" s="1" t="n">
+      <c r="I494" s="3" t="n">
         <v>-104.61628</v>
       </c>
-      <c r="J494" s="1" t="s">
+      <c r="J494" s="3" t="s">
         <v>2557</v>
       </c>
-      <c r="K494" s="1" t="s">
+      <c r="K494" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="L494" s="3"/>
     </row>
     <row r="495" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="1" t="n">
@@ -25581,7 +25620,7 @@
         <v>2562</v>
       </c>
       <c r="K495" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25616,80 +25655,80 @@
         <v>2567</v>
       </c>
       <c r="K496" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="1" t="n">
         <v>133</v>
       </c>
-      <c r="B497" s="3" t="s">
+      <c r="B497" s="5" t="s">
         <v>2568</v>
       </c>
-      <c r="C497" s="3" t="s">
+      <c r="C497" s="5" t="s">
         <v>2569</v>
       </c>
-      <c r="D497" s="3" t="s">
+      <c r="D497" s="5" t="s">
         <v>2570</v>
       </c>
-      <c r="E497" s="3" t="s">
+      <c r="E497" s="5" t="s">
         <v>2513</v>
       </c>
-      <c r="F497" s="3" t="s">
+      <c r="F497" s="5" t="s">
         <v>2571</v>
       </c>
-      <c r="G497" s="3" t="s">
+      <c r="G497" s="5" t="s">
         <v>2572</v>
       </c>
-      <c r="H497" s="3" t="n">
+      <c r="H497" s="5" t="n">
         <v>52.147586</v>
       </c>
-      <c r="I497" s="3" t="n">
+      <c r="I497" s="5" t="n">
         <v>-106.61636</v>
       </c>
-      <c r="J497" s="3" t="s">
+      <c r="J497" s="5" t="s">
         <v>2573</v>
       </c>
-      <c r="K497" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L497" s="3"/>
+      <c r="K497" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L497" s="5"/>
     </row>
     <row r="498" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="1" t="n">
         <v>296</v>
       </c>
-      <c r="B498" s="3" t="s">
+      <c r="B498" s="5" t="s">
         <v>2574</v>
       </c>
-      <c r="C498" s="3" t="s">
+      <c r="C498" s="5" t="s">
         <v>2575</v>
       </c>
-      <c r="D498" s="3" t="s">
+      <c r="D498" s="5" t="s">
         <v>2570</v>
       </c>
-      <c r="E498" s="3" t="s">
+      <c r="E498" s="5" t="s">
         <v>2513</v>
       </c>
-      <c r="F498" s="3" t="s">
+      <c r="F498" s="5" t="s">
         <v>2576</v>
       </c>
-      <c r="G498" s="3" t="s">
+      <c r="G498" s="5" t="s">
         <v>2577</v>
       </c>
-      <c r="H498" s="3" t="n">
+      <c r="H498" s="5" t="n">
         <v>52.132139</v>
       </c>
-      <c r="I498" s="3" t="n">
+      <c r="I498" s="5" t="n">
         <v>-106.720591</v>
       </c>
-      <c r="J498" s="3" t="s">
+      <c r="J498" s="5" t="s">
         <v>2578</v>
       </c>
-      <c r="K498" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L498" s="3"/>
+      <c r="K498" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L498" s="5"/>
     </row>
     <row r="499" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="1" t="n">
@@ -25761,40 +25800,41 @@
         <v>23</v>
       </c>
     </row>
-    <row r="501" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A501" s="1" t="n">
+    <row r="501" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A501" s="3" t="n">
         <v>287</v>
       </c>
-      <c r="B501" s="1" t="s">
+      <c r="B501" s="3" t="s">
         <v>2589</v>
       </c>
-      <c r="C501" s="1" t="s">
+      <c r="C501" s="3" t="s">
         <v>2590</v>
       </c>
-      <c r="D501" s="1" t="s">
+      <c r="D501" s="3" t="s">
         <v>2589</v>
       </c>
-      <c r="E501" s="1" t="s">
+      <c r="E501" s="3" t="s">
         <v>2513</v>
       </c>
-      <c r="F501" s="1" t="s">
+      <c r="F501" s="3" t="s">
         <v>2591</v>
       </c>
-      <c r="G501" s="1" t="s">
+      <c r="G501" s="3" t="s">
         <v>2592</v>
       </c>
-      <c r="H501" s="1" t="n">
+      <c r="H501" s="3" t="n">
         <v>51.211644</v>
       </c>
-      <c r="I501" s="1" t="n">
+      <c r="I501" s="3" t="n">
         <v>-102.441011</v>
       </c>
-      <c r="J501" s="1" t="s">
+      <c r="J501" s="3" t="s">
         <v>2593</v>
       </c>
-      <c r="K501" s="1" t="s">
+      <c r="K501" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="L501" s="3"/>
     </row>
     <row r="502" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="1" t="n">
